--- a/results/job_matches_2026-07-13.xlsx
+++ b/results/job_matches_2026-07-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,33 +503,103 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Reliability Engineer, Battery Module</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Sparks, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, dbt, Power BI, Tableau, CI/CD</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3af907c177dd5fdb</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>SQL Developer</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>We Are Recruiting</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Foley, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39a0bb69f0f00f0c</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>Oracle OCI Cloud Engineer</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Lateral Insights</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Great Falls, VA, US USA</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D5" t="n">
         <v>11.8</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ed69d2e91eede4e0</t>
         </is>

--- a/results/job_matches_2026-07-13.xlsx
+++ b/results/job_matches_2026-07-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,140 +468,700 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data and Analytics Engineer</t>
+          <t>Senior Software Engineer – Full Stack (Java, AWS, React)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Digital Strategy LLC</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd127ae8715c196f</t>
+          <t>https://www.indeed.com/viewjob?jk=d0f99e44e51085df</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Reliability Engineer, Battery Module</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Astronautics Corporation of America</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sparks, NV, US USA</t>
+          <t>Oak Creek, WI, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af907c177dd5fdb</t>
+          <t>https://www.indeed.com/viewjob?jk=9d06ee741990db6b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SQL Developer</t>
+          <t>Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>We Are Recruiting</t>
+          <t>Digital Strategy LLC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Foley, AL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a0bb69f0f00f0c</t>
+          <t>https://www.indeed.com/viewjob?jk=cd127ae8715c196f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Oracle, SQL Server</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2afd6091c64d55df</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Reliability Engineer, Battery Module</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Sparks, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, dbt, Power BI, Tableau, CI/CD</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3af907c177dd5fdb</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SQL Developer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>We Are Recruiting</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Foley, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39a0bb69f0f00f0c</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Westminster, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26c2fa1d45c9055b</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Big Data)</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Westminster, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4d8e19f0fb16bc7</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Data Architect - C2H - Onsite</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>TEEMA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Flower Mound, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7356e10af404cb1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kimball Midwest</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2dd6388cdeebf986</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Redshift, S3, Azure, Scala, PostgreSQL, MLOps, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=622d3a3e3c903762</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Data Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AWS, Databricks, Hadoop, HDFS, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad3836b0fc7c4571</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>Oracle OCI Cloud Engineer</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Lateral Insights</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Great Falls, VA, US USA</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D14" t="n">
         <v>11.8</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ed69d2e91eede4e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, RDS, Databricks, Unity Catalog, Spark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57668a6af42a8310</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Analyst, Data Engineering</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark, Scala, ETL</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=29d151c251dc07f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5962ad63a23cfa81</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=083794db905029d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81752facbba9d16c</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior AI &amp; Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e3b212b4def3f9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Full Stack Mid-level Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>WSFS Bank</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Wilmington, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Terraform, Kubernetes, Datadog, Python</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=78f65e99062ef281</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-13.xlsx
+++ b/results/job_matches_2026-07-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Senior Software Engineer (Big Data)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Smart Apply Test Company</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, HDFS, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Hadoop, Hive, Spark, Scala, Data Modeling, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3836b0fc7c4571</t>
+          <t>https://www.indeed.com/viewjob?jk=17f9d9276b923717</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Oracle OCI Cloud Engineer</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lateral Insights</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Great Falls, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,17 +906,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Databricks, Hadoop, HDFS, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed69d2e91eede4e0</t>
+          <t>https://www.indeed.com/viewjob?jk=ad3836b0fc7c4571</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineering</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Applied Medical</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rancho Santa Margarita, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,24 +976,24 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, YARN, SQL Server, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29d151c251dc07f6</t>
+          <t>https://www.indeed.com/viewjob?jk=c3004d47870448a1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Analyst, Data Engineering</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1003,25 +1003,25 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
+          <t>Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5962ad63a23cfa81</t>
+          <t>https://www.indeed.com/viewjob?jk=29d151c251dc07f6</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=083794db905029d1</t>
+          <t>https://www.indeed.com/viewjob?jk=5962ad63a23cfa81</t>
         </is>
       </c>
     </row>
@@ -1073,37 +1073,37 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81752facbba9d16c</t>
+          <t>https://www.indeed.com/viewjob?jk=083794db905029d1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior AI &amp; Cloud Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Smart Apply Test Company</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e3b212b4def3f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=2d697f334d121ec3</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Full Stack Mid-level Java Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>WSFS Bank</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,15 +1151,85 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81752facbba9d16c</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior AI &amp; Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e3b212b4def3f9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Full Stack Mid-level Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>WSFS Bank</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Wilmington, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Terraform, Kubernetes, Datadog, Python</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=78f65e99062ef281</t>
         </is>

--- a/results/job_matches_2026-07-13.xlsx
+++ b/results/job_matches_2026-07-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Big Data)</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Clifton, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d8e19f0fb16bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=009aa09bd21a9217</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Architect - C2H - Onsite</t>
+          <t>Senior Software Engineer (Big Data)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TEEMA</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,52 +766,52 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7356e10af404cb1</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d8e19f0fb16bc7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect - C2H - Onsite</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>TEEMA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd6388cdeebf986</t>
+          <t>https://www.indeed.com/viewjob?jk=e7356e10af404cb1</t>
         </is>
       </c>
     </row>
@@ -823,12 +823,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,69 +836,69 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, Azure, Scala, PostgreSQL, MLOps, CI/CD, Azure DevOps</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=622d3a3e3c903762</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd6388cdeebf986</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Big Data)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Smart Apply Test Company</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Hive, Spark, Scala, Data Modeling, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, S3, Azure, Scala, PostgreSQL, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17f9d9276b923717</t>
+          <t>https://www.indeed.com/viewjob?jk=622d3a3e3c903762</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Senior Software Engineer (Big Data)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Smart Apply Test Company</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,24 +906,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, HDFS, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Hadoop, Hive, Spark, Scala, Data Modeling, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3836b0fc7c4571</t>
+          <t>https://www.indeed.com/viewjob?jk=17f9d9276b923717</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Databricks, Unity Catalog, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Databricks, Hadoop, HDFS, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57668a6af42a8310</t>
+          <t>https://www.indeed.com/viewjob?jk=ad3836b0fc7c4571</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Oracle OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Applied Medical</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Rancho Santa Margarita, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, YARN, SQL Server, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,14 +986,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3004d47870448a1</t>
+          <t>https://www.indeed.com/viewjob?jk=05cf4bb1193bec3f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineering</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,59 +1011,59 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, Glue, Redshift, RDS, Databricks, Unity Catalog, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29d151c251dc07f6</t>
+          <t>https://www.indeed.com/viewjob?jk=57668a6af42a8310</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Applied Medical</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Rancho Santa Margarita, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
+          <t>AWS, RDS, Azure, YARN, SQL Server, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5962ad63a23cfa81</t>
+          <t>https://www.indeed.com/viewjob?jk=c3004d47870448a1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Analyst, Data Engineering</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1073,25 +1073,25 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
+          <t>Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark, Scala, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=083794db905029d1</t>
+          <t>https://www.indeed.com/viewjob?jk=29d151c251dc07f6</t>
         </is>
       </c>
     </row>
@@ -1103,30 +1103,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Smart Apply Test Company</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d697f334d121ec3</t>
+          <t>https://www.indeed.com/viewjob?jk=5962ad63a23cfa81</t>
         </is>
       </c>
     </row>
@@ -1143,37 +1143,37 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81752facbba9d16c</t>
+          <t>https://www.indeed.com/viewjob?jk=083794db905029d1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior AI &amp; Cloud Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Smart Apply Test Company</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e3b212b4def3f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=2d697f334d121ec3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Full Stack Mid-level Java Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WSFS Bank</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,15 +1221,85 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81752facbba9d16c</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior AI &amp; Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e3b212b4def3f9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Full Stack Mid-level Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>WSFS Bank</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Wilmington, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Terraform, Kubernetes, Datadog, Python</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=78f65e99062ef281</t>
         </is>

--- a/results/job_matches_2026-07-13.xlsx
+++ b/results/job_matches_2026-07-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Full Stack (Java, AWS, React)</t>
+          <t>Senior Software Engineer (Data Engineering and Infrastructure)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Aurora Innovation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,182 +486,182 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, Scala, Kafka, MySQL</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, Azure, GCP, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0f99e44e51085df</t>
+          <t>https://www.indeed.com/viewjob?jk=b6b8b74c1db36b82</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Senior Software Engineer – Full Stack (Java, AWS, React)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Astronautics Corporation of America</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Oak Creek, WI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d06ee741990db6b</t>
+          <t>https://www.indeed.com/viewjob?jk=d0f99e44e51085df</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data and Analytics Engineer</t>
+          <t>Software Engineer I (Data Eng infra)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Digital Strategy LLC</t>
+          <t>Aurora Innovation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Glue, Kinesis, Redshift, S3, Azure, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd127ae8715c196f</t>
+          <t>https://www.indeed.com/viewjob?jk=490f497f5639497d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Astronautics Corporation of America</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oak Creek, WI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2afd6091c64d55df</t>
+          <t>https://www.indeed.com/viewjob?jk=9d06ee741990db6b</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Reliability Engineer, Battery Module</t>
+          <t>Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Digital Strategy LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sparks, NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af907c177dd5fdb</t>
+          <t>https://www.indeed.com/viewjob?jk=cd127ae8715c196f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SQL Developer</t>
+          <t>DATABASE ADMINISTRATOR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>We Are Recruiting</t>
+          <t>Versant Power</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Foley, AL, US USA</t>
+          <t>Bangor, ME, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a0bb69f0f00f0c</t>
+          <t>https://www.indeed.com/viewjob?jk=e0bb056d66ba0554</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,120 +688,120 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26c2fa1d45c9055b</t>
+          <t>https://www.indeed.com/viewjob?jk=2afd6091c64d55df</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Reliability Engineer, Battery Module</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Clifton, NJ, US USA</t>
+          <t>Sparks, NV, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009aa09bd21a9217</t>
+          <t>https://www.indeed.com/viewjob?jk=3af907c177dd5fdb</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Big Data)</t>
+          <t>Engineering Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d8e19f0fb16bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=e831741c10ec9a8d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Architect - C2H - Onsite</t>
+          <t>SQL Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TEEMA</t>
+          <t>We Are Recruiting</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>Foley, AL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,49 +811,49 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7356e10af404cb1</t>
+          <t>https://www.indeed.com/viewjob?jk=39a0bb69f0f00f0c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SAP BTP / MCP Solution Consultant @Remote</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>Source Code Technology</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd6388cdeebf986</t>
+          <t>https://www.indeed.com/viewjob?jk=ad9fbd068e4b0061</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,37 +863,37 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, Azure, Scala, PostgreSQL, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=622d3a3e3c903762</t>
+          <t>https://www.indeed.com/viewjob?jk=41b78df5b95306be</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Big Data)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Smart Apply Test Company</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -902,406 +902,1211 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Hive, Spark, Scala, Data Modeling, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17f9d9276b923717</t>
+          <t>https://www.indeed.com/viewjob?jk=26c2fa1d45c9055b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Clifton, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, HDFS, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3836b0fc7c4571</t>
+          <t>https://www.indeed.com/viewjob?jk=009aa09bd21a9217</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Oracle OCI Cloud Engineer</t>
+          <t>Senior Software Engineer (Big Data)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05cf4bb1193bec3f</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d8e19f0fb16bc7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II - Enterprise AI Products</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Databricks, Unity Catalog, Spark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57668a6af42a8310</t>
+          <t>https://www.indeed.com/viewjob?jk=9dcac0248b7373d4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Data Architect - C2H - Onsite</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Applied Medical</t>
+          <t>TEEMA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Rancho Santa Margarita, CA, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, YARN, SQL Server, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3004d47870448a1</t>
+          <t>https://www.indeed.com/viewjob?jk=e7356e10af404cb1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Analyst, Data Engineering</t>
+          <t>Technical Specialist(Python Developer)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Glue, Lambda, Redshift, S3, RDS, Databricks, Spark, PySpark, Scala, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29d151c251dc07f6</t>
+          <t>https://www.indeed.com/viewjob?jk=d26e04dc07674449</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior System Software Engineer for Cloud – GeForce NOW</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, DynamoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5962ad63a23cfa81</t>
+          <t>https://www.indeed.com/viewjob?jk=9d6d30e78e6f4c6e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=083794db905029d1</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd6388cdeebf986</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Smart Apply Test Company</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, S3, Azure, Scala, PostgreSQL, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d697f334d121ec3</t>
+          <t>https://www.indeed.com/viewjob?jk=622d3a3e3c903762</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Technical Specialist - Senior</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81752facbba9d16c</t>
+          <t>https://www.indeed.com/viewjob?jk=51d97fe985e82f06</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior AI &amp; Cloud Engineer</t>
+          <t>Mgr, Data Platform Engineering</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>University Federal Credit Union</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e3b212b4def3f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=4a64cdbde4f50734</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>Senior Data Scientist - GenAI/Agentic AI - Remote</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Molina Healthcare</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=34b1a1a8543d5bde</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Big Data)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Smart Apply Test Company</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Westminster, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Hadoop, Hive, Spark, Scala, Data Modeling, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=17f9d9276b923717</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Data Solutions Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AWS, Databricks, Hadoop, HDFS, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad3836b0fc7c4571</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Oracle OCI Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>American business solutions inc</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=05cf4bb1193bec3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, RDS, Databricks, Unity Catalog, Spark, Scala, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57668a6af42a8310</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Application Developer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Applied Medical</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Rancho Santa Margarita, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, YARN, SQL Server, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3004d47870448a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Threat Detection Engineer – Security Operations</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ID.me</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=845986ee9c384d0c</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Threat Detection Engineer – Security Operations</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ID.me</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb9bc641ca30ce01</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5962ad63a23cfa81</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=083794db905029d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Data Engineer - Oracle data integrator and BI</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4b40de561865171b</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>C.H. Robinson</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14d4be214d89c9f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>C.H. Robinson</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3fd7b858f4e17691</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Master Data Management (MDM) Architect</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AWS, Glue, S3, RDS, Azure, Databricks, GCP, Dataflow, Scala, Snowflake</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1d0e0294ddfbe996</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Data Architect / Quality Assurance Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>City of Philadelphia, PA</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d0882144e65f22c</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>C.H. Robinson</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c90454ed63602f69</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Generative AI Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Afficiency</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MLflow, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=be5a298b53e539ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Smart Apply Test Company</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d697f334d121ec3</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81752facbba9d16c</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Senior Data Integration Operations Engineerr</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Northeastern University</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Snowflake, Informatica PowerCenter, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=748fc639b3268939</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Senior AI &amp; Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e3b212b4def3f9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
           <t>Full Stack Mid-level Java Software Engineer</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>WSFS Bank</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Wilmington, DE, US USA</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D46" t="n">
         <v>10.4</v>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Terraform, Kubernetes, Datadog, Python</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=78f65e99062ef281</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Level 2 – Technical Support Engineer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, ELT, REST API integration</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f92c2bb95c010dd6</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Bi Developer</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Cloud and Things</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Albany, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, Data Modeling, Star Schema, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b85dd5750a229b32</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-13.xlsx
+++ b/results/job_matches_2026-07-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data and Analytics Engineer</t>
+          <t>DATABASE ADMINISTRATOR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Digital Strategy LLC</t>
+          <t>Versant Power</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bangor, ME, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,69 +626,69 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd127ae8715c196f</t>
+          <t>https://www.indeed.com/viewjob?jk=e0bb056d66ba0554</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DATABASE ADMINISTRATOR</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Versant Power</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bangor, ME, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0bb056d66ba0554</t>
+          <t>https://www.indeed.com/viewjob?jk=2afd6091c64d55df</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Reliability Engineer, Battery Module</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sparks, NV, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2afd6091c64d55df</t>
+          <t>https://www.indeed.com/viewjob?jk=3af907c177dd5fdb</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Reliability Engineer, Battery Module</t>
+          <t>Engineering Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sparks, NV, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af907c177dd5fdb</t>
+          <t>https://www.indeed.com/viewjob?jk=e831741c10ec9a8d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Engineering Architect</t>
+          <t>SQL Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>We Are Recruiting</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Foley, AL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e831741c10ec9a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=39a0bb69f0f00f0c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SQL Developer</t>
+          <t>SAP BTP / MCP Solution Consultant @Remote</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>We Are Recruiting</t>
+          <t>Source Code Technology</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Foley, AL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a0bb69f0f00f0c</t>
+          <t>https://www.indeed.com/viewjob?jk=ad9fbd068e4b0061</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SAP BTP / MCP Solution Consultant @Remote</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Source Code Technology</t>
+          <t>Vytalize Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, IAM, RDS, Databricks, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad9fbd068e4b0061</t>
+          <t>https://www.indeed.com/viewjob?jk=439c58ad35a8bb78</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1063,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Technical Specialist(Python Developer)</t>
+          <t>Technical Specialist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d26e04dc07674449</t>
+          <t>https://www.indeed.com/viewjob?jk=91e03219acd75f33</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior System Software Engineer for Cloud – GeForce NOW</t>
+          <t>Technical Specialist(Python Developer)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, DynamoDB, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d6d30e78e6f4c6e</t>
+          <t>https://www.indeed.com/viewjob?jk=d26e04dc07674449</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer I-Pathology Molecular and Cell Based Medicine</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd6388cdeebf986</t>
+          <t>https://www.indeed.com/viewjob?jk=1f1090f617db00fd</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior System Software Engineer for Cloud – GeForce NOW</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, Azure, Scala, PostgreSQL, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, DynamoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=622d3a3e3c903762</t>
+          <t>https://www.indeed.com/viewjob?jk=9d6d30e78e6f4c6e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Technical Specialist - Senior</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51d97fe985e82f06</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd6388cdeebf986</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Mgr, Data Platform Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>University Federal Credit Union</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,42 +1256,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, Redshift, S3, Azure, Scala, PostgreSQL, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a64cdbde4f50734</t>
+          <t>https://www.indeed.com/viewjob?jk=622d3a3e3c903762</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - GenAI/Agentic AI - Remote</t>
+          <t>Technical Specialist - Senior</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34b1a1a8543d5bde</t>
+          <t>https://www.indeed.com/viewjob?jk=9cfb170c35e948ca</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Big Data)</t>
+          <t>Technical Specialist - Senior</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Smart Apply Test Company</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Hive, Spark, Scala, Data Modeling, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,59 +1336,59 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17f9d9276b923717</t>
+          <t>https://www.indeed.com/viewjob?jk=51d97fe985e82f06</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Mgr, Data Platform Engineering</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>University Federal Credit Union</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, HDFS, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3836b0fc7c4571</t>
+          <t>https://www.indeed.com/viewjob?jk=4a64cdbde4f50734</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Oracle OCI Cloud Engineer</t>
+          <t>Senior Data Scientist - GenAI/Agentic AI - Remote</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05cf4bb1193bec3f</t>
+          <t>https://www.indeed.com/viewjob?jk=34b1a1a8543d5bde</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer (Big Data)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Smart Apply Test Company</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Databricks, Unity Catalog, Spark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Hadoop, Hive, Spark, Scala, Data Modeling, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57668a6af42a8310</t>
+          <t>https://www.indeed.com/viewjob?jk=17f9d9276b923717</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Applied Medical</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Rancho Santa Margarita, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, YARN, SQL Server, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Databricks, Hadoop, HDFS, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3004d47870448a1</t>
+          <t>https://www.indeed.com/viewjob?jk=ad3836b0fc7c4571</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>NYSTEC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=845986ee9c384d0c</t>
+          <t>https://www.indeed.com/viewjob?jk=e43f810dbefdcbc9</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,49 +1546,49 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb9bc641ca30ce01</t>
+          <t>https://www.indeed.com/viewjob?jk=91f681ba8c58e14f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Oracle OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5962ad63a23cfa81</t>
+          <t>https://www.indeed.com/viewjob?jk=05cf4bb1193bec3f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1598,147 +1598,147 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
+          <t>AWS, Glue, Redshift, RDS, Databricks, Unity Catalog, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=083794db905029d1</t>
+          <t>https://www.indeed.com/viewjob?jk=57668a6af42a8310</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer - Oracle data integrator and BI</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Applied Medical</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rancho Santa Margarita, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, YARN, SQL Server, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b40de561865171b</t>
+          <t>https://www.indeed.com/viewjob?jk=c3004d47870448a1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Threat Detection Engineer – Security Operations</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d4be214d89c9f3</t>
+          <t>https://www.indeed.com/viewjob?jk=845986ee9c384d0c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Threat Detection Engineer – Security Operations</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fd7b858f4e17691</t>
+          <t>https://www.indeed.com/viewjob?jk=bb9bc641ca30ce01</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Master Data Management (MDM) Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, Databricks, GCP, Dataflow, Scala, Snowflake</t>
+          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d0e0294ddfbe996</t>
+          <t>https://www.indeed.com/viewjob?jk=5962ad63a23cfa81</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Architect / Quality Assurance Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>City of Philadelphia, PA</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Airflow, Git</t>
+          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d0882144e65f22c</t>
+          <t>https://www.indeed.com/viewjob?jk=083794db905029d1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Data Engineer - Oracle data integrator and BI</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
+          <t>RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90454ed63602f69</t>
+          <t>https://www.indeed.com/viewjob?jk=4b40de561865171b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Afficiency</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,112 +1851,112 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MLflow, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be5a298b53e539ed</t>
+          <t>https://www.indeed.com/viewjob?jk=14d4be214d89c9f3</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Smart Apply Test Company</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d697f334d121ec3</t>
+          <t>https://www.indeed.com/viewjob?jk=3fd7b858f4e17691</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Architect of Data Architecture</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Empower</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, Redshift, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81752facbba9d16c</t>
+          <t>https://www.indeed.com/viewjob?jk=2a69b442d48a997e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Integration Operations Engineerr</t>
+          <t>Senior Master Data Management (MDM) Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Snowflake, Informatica PowerCenter, ETL, ELT</t>
+          <t>AWS, Glue, S3, RDS, Azure, Databricks, GCP, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,102 +1966,102 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=748fc639b3268939</t>
+          <t>https://www.indeed.com/viewjob?jk=1d0e0294ddfbe996</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior AI &amp; Cloud Engineer</t>
+          <t>Data Architect / Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>City of Philadelphia, PA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>RDS, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e3b212b4def3f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=2d0882144e65f22c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Full Stack Mid-level Java Software Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>WSFS Bank</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Terraform, Kubernetes, Datadog, Python</t>
+          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78f65e99062ef281</t>
+          <t>https://www.indeed.com/viewjob?jk=c90454ed63602f69</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Level 2 – Technical Support Engineer</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Afficiency</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, ELT, REST API integration</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MLflow, Terraform, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f92c2bb95c010dd6</t>
+          <t>https://www.indeed.com/viewjob?jk=be5a298b53e539ed</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Bi Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>Smart Apply Test Company</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,17 +2096,297 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d697f334d121ec3</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81752facbba9d16c</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer – Enterprise, Data &amp; AI</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Zoox</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Foster City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, Terraform, Kubernetes, Airflow</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=303390f40d7bb17a</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Senior Data Integration Operations Engineerr</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Northeastern University</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Snowflake, Informatica PowerCenter, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=748fc639b3268939</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Senior AI &amp; Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e3b212b4def3f9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Data Engineer - &amp; Modeler Informatica</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aebf504e442ce2f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Full Stack Mid-level Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>WSFS Bank</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Wilmington, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Terraform, Kubernetes, Datadog, Python</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=78f65e99062ef281</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Bi Developer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Cloud and Things</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Albany, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Oracle, SQL Server, Data Modeling, Star Schema, ETL, Power BI, Tableau</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b85dd5750a229b32</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Level 2 – Technical Support Engineer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, ELT, REST API integration</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f92c2bb95c010dd6</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-13.xlsx
+++ b/results/job_matches_2026-07-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G56"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Engineering and Infrastructure)</t>
+          <t>Databricks Solution Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Aurora Innovation</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>22.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, Azure, GCP, BigQuery, Spark</t>
+          <t>AWS, Kinesis, S3, IAM, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6b8b74c1db36b82</t>
+          <t>https://www.indeed.com/viewjob?jk=95200cc7178deeb2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Full Stack (Java, AWS, React)</t>
+          <t>Senior Software Engineer (Data Engineering and Infrastructure)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Aurora Innovation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,69 +521,69 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, Scala, Kafka, MySQL</t>
+          <t>AWS, Glue, EMR, Kinesis, Redshift, S3, Azure, GCP, BigQuery, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0f99e44e51085df</t>
+          <t>https://www.indeed.com/viewjob?jk=b6b8b74c1db36b82</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer I (Data Eng infra)</t>
+          <t>Senior Software Engineer – Full Stack (Java, AWS, React)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Aurora Innovation</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, S3, Azure, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Azure, Scala, Kafka, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=490f497f5639497d</t>
+          <t>https://www.indeed.com/viewjob?jk=d0f99e44e51085df</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Software Engineer I (Data Eng infra)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Astronautics Corporation of America</t>
+          <t>Aurora Innovation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Oak Creek, WI, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,104 +591,104 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Kinesis, Redshift, S3, Azure, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d06ee741990db6b</t>
+          <t>https://www.indeed.com/viewjob?jk=490f497f5639497d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DATABASE ADMINISTRATOR</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Versant Power</t>
+          <t>Astronautics Corporation of America</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bangor, ME, US USA</t>
+          <t>Oak Creek, WI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, BigQuery, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0bb056d66ba0554</t>
+          <t>https://www.indeed.com/viewjob?jk=9d06ee741990db6b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DATABASE ADMINISTRATOR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Versant Power</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bangor, ME, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2afd6091c64d55df</t>
+          <t>https://www.indeed.com/viewjob?jk=e0bb056d66ba0554</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Reliability Engineer, Battery Module</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sparks, NV, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,42 +696,42 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af907c177dd5fdb</t>
+          <t>https://www.indeed.com/viewjob?jk=2afd6091c64d55df</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Engineering Architect</t>
+          <t>Reliability Engineer, Battery Module</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Sparks, NV, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e831741c10ec9a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=3af907c177dd5fdb</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SQL Developer</t>
+          <t>AWS Data Engineering Advisor</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>We Are Recruiting</t>
+          <t>ENGIE</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Foley, AL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Glue, Kinesis, Athena, S3, ECS, IAM, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a0bb69f0f00f0c</t>
+          <t>https://www.indeed.com/viewjob?jk=088581dbc2434494</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SAP BTP / MCP Solution Consultant @Remote</t>
+          <t>Engineering Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Source Code Technology</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, ECS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad9fbd068e4b0061</t>
+          <t>https://www.indeed.com/viewjob?jk=e831741c10ec9a8d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>SQL Developer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vytalize Health</t>
+          <t>We Are Recruiting</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Foley, AL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, IAM, RDS, Databricks, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439c58ad35a8bb78</t>
+          <t>https://www.indeed.com/viewjob?jk=39a0bb69f0f00f0c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Vytalize Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,24 +871,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, IAM, RDS, Databricks, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41b78df5b95306be</t>
+          <t>https://www.indeed.com/viewjob?jk=439c58ad35a8bb78</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26c2fa1d45c9055b</t>
+          <t>https://www.indeed.com/viewjob?jk=41b78df5b95306be</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Clifton, NJ, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Oracle</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009aa09bd21a9217</t>
+          <t>https://www.indeed.com/viewjob?jk=26c2fa1d45c9055b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Big Data)</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Clifton, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d8e19f0fb16bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=009aa09bd21a9217</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer II - Enterprise AI Products</t>
+          <t>Senior Software Engineer (Big Data)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dcac0248b7373d4</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d8e19f0fb16bc7</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Architect - C2H - Onsite</t>
+          <t>Software Engineer II - Enterprise AI Products</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TEEMA</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7356e10af404cb1</t>
+          <t>https://www.indeed.com/viewjob?jk=9dcac0248b7373d4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Technical Specialist</t>
+          <t>Data Architect - C2H - Onsite</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>TEEMA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91e03219acd75f33</t>
+          <t>https://www.indeed.com/viewjob?jk=e7356e10af404cb1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Technical Specialist(Python Developer)</t>
+          <t>Senior Financial Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>The Research Foundation for The State University of New York at Stony Brook</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Stony Brook, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d26e04dc07674449</t>
+          <t>https://www.indeed.com/viewjob?jk=05c72e69c8d1b5df</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer I-Pathology Molecular and Cell Based Medicine</t>
+          <t>Technical Specialist</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f1090f617db00fd</t>
+          <t>https://www.indeed.com/viewjob?jk=91e03219acd75f33</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior System Software Engineer for Cloud – GeForce NOW</t>
+          <t>Technical Specialist(Python Developer)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, DynamoDB, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d6d30e78e6f4c6e</t>
+          <t>https://www.indeed.com/viewjob?jk=d26e04dc07674449</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer I-Pathology Molecular and Cell Based Medicine</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd6388cdeebf986</t>
+          <t>https://www.indeed.com/viewjob?jk=1f1090f617db00fd</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Data Engineer, Cat Digital</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, Azure, Scala, PostgreSQL, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, Azure, Scala, Snowflake, Power BI, CI/CD, Azure DevOps, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=622d3a3e3c903762</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba56e26d2f7d66e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Technical Specialist - Senior</t>
+          <t>Senior System Software Engineer for Cloud – GeForce NOW</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, DynamoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cfb170c35e948ca</t>
+          <t>https://www.indeed.com/viewjob?jk=9d6d30e78e6f4c6e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Technical Specialist - Senior</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51d97fe985e82f06</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd6388cdeebf986</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Mgr, Data Platform Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>University Federal Credit Union</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,42 +1361,42 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, Redshift, S3, Azure, Scala, PostgreSQL, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a64cdbde4f50734</t>
+          <t>https://www.indeed.com/viewjob?jk=622d3a3e3c903762</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - GenAI/Agentic AI - Remote</t>
+          <t>Technical Specialist - Senior</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34b1a1a8543d5bde</t>
+          <t>https://www.indeed.com/viewjob?jk=9cfb170c35e948ca</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Big Data)</t>
+          <t>Technical Specialist - Senior</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Smart Apply Test Company</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Hive, Spark, Scala, Data Modeling, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17f9d9276b923717</t>
+          <t>https://www.indeed.com/viewjob?jk=51d97fe985e82f06</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Senior Data Scientist - GenAI/Agentic AI - Remote</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, HDFS, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3836b0fc7c4571</t>
+          <t>https://www.indeed.com/viewjob?jk=34b1a1a8543d5bde</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer (Big Data)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NYSTEC</t>
+          <t>Smart Apply Test Company</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Databricks, Hadoop, Hive, Spark, Scala, Data Modeling, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e43f810dbefdcbc9</t>
+          <t>https://www.indeed.com/viewjob?jk=17f9d9276b923717</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Databricks, Hadoop, HDFS, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f681ba8c58e14f</t>
+          <t>https://www.indeed.com/viewjob?jk=ad3836b0fc7c4571</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Oracle OCI Cloud Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>FirstDay Foundation</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05cf4bb1193bec3f</t>
+          <t>https://www.indeed.com/viewjob?jk=d797cade2cc30f67</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>NYSTEC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Databricks, Unity Catalog, Spark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57668a6af42a8310</t>
+          <t>https://www.indeed.com/viewjob?jk=e43f810dbefdcbc9</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Applied Medical</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Rancho Santa Margarita, CA, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, YARN, SQL Server, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3004d47870448a1</t>
+          <t>https://www.indeed.com/viewjob?jk=91f681ba8c58e14f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Oracle OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=845986ee9c384d0c</t>
+          <t>https://www.indeed.com/viewjob?jk=05cf4bb1193bec3f</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,174 +1711,174 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, Glue, Redshift, RDS, Databricks, Unity Catalog, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb9bc641ca30ce01</t>
+          <t>https://www.indeed.com/viewjob?jk=57668a6af42a8310</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Managing Engineer - Fusion GRC Platform</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Scala, ETL, ELT, Splunk, CI/CD, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5962ad63a23cfa81</t>
+          <t>https://www.indeed.com/viewjob?jk=fb8c6087cd256e74</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Applied Medical</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Rancho Santa Margarita, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
+          <t>AWS, RDS, Azure, YARN, SQL Server, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=083794db905029d1</t>
+          <t>https://www.indeed.com/viewjob?jk=c3004d47870448a1</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer - Oracle data integrator and BI</t>
+          <t>Threat Detection Engineer – Security Operations</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b40de561865171b</t>
+          <t>https://www.indeed.com/viewjob?jk=845986ee9c384d0c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Threat Detection Engineer – Security Operations</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d4be214d89c9f3</t>
+          <t>https://www.indeed.com/viewjob?jk=bb9bc641ca30ce01</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. IT Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
+          <t>API Gateway, RDS, Hadoop, HBase, Scala, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fd7b858f4e17691</t>
+          <t>https://www.indeed.com/viewjob?jk=d0debfb86cec6f81</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Architect of Data Architecture</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Empower</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a69b442d48a997e</t>
+          <t>https://www.indeed.com/viewjob?jk=18e522d64598216a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Master Data Management (MDM) Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, Databricks, GCP, Dataflow, Scala, Snowflake</t>
+          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d0e0294ddfbe996</t>
+          <t>https://www.indeed.com/viewjob?jk=5962ad63a23cfa81</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Architect / Quality Assurance Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>City of Philadelphia, PA</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Airflow, Git</t>
+          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d0882144e65f22c</t>
+          <t>https://www.indeed.com/viewjob?jk=083794db905029d1</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Marketing Technology Strategist</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Phase2</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90454ed63602f69</t>
+          <t>https://www.indeed.com/viewjob?jk=08cde2c4527579db</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Data Engineer - Oracle data integrator and BI</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Afficiency</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,112 +2061,112 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MLflow, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be5a298b53e539ed</t>
+          <t>https://www.indeed.com/viewjob?jk=4b40de561865171b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Smart Apply Test Company</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d697f334d121ec3</t>
+          <t>https://www.indeed.com/viewjob?jk=14d4be214d89c9f3</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81752facbba9d16c</t>
+          <t>https://www.indeed.com/viewjob?jk=3fd7b858f4e17691</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise, Data &amp; AI</t>
+          <t>Solutions Architect - Financial Services (Hunter)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Zoox</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, Terraform, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303390f40d7bb17a</t>
+          <t>https://www.indeed.com/viewjob?jk=4b1f7af295967ab5</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Integration Operations Engineerr</t>
+          <t>Senior Security Architect(AI)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Paylocity</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Snowflake, Informatica PowerCenter, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,102 +2211,102 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=748fc639b3268939</t>
+          <t>https://www.indeed.com/viewjob?jk=0ffe1515831234d9</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior AI &amp; Cloud Engineer</t>
+          <t>Product Engineer - Fusion GRC Platform</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, ETL, ELT, Splunk, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e3b212b4def3f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=ef44df6379fa49ce</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer - &amp; Modeler Informatica</t>
+          <t>Architect of Data Architecture</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Empower</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>AWS, Kinesis, Redshift, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aebf504e442ce2f2</t>
+          <t>https://www.indeed.com/viewjob?jk=2a69b442d48a997e</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Full Stack Mid-level Java Software Engineer</t>
+          <t>Senior Master Data Management (MDM) Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>WSFS Bank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Terraform, Kubernetes, Datadog, Python</t>
+          <t>AWS, Glue, S3, RDS, Azure, Databricks, GCP, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78f65e99062ef281</t>
+          <t>https://www.indeed.com/viewjob?jk=1d0e0294ddfbe996</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Bi Developer</t>
+          <t>Data Architect / Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>City of Philadelphia, PA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, Data Modeling, Star Schema, ETL, Power BI, Tableau</t>
+          <t>RDS, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,42 +2351,567 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b85dd5750a229b32</t>
+          <t>https://www.indeed.com/viewjob?jk=2d0882144e65f22c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>C.H. Robinson</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c90454ed63602f69</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer - SRE</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Bitscopic</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=91f2cb5787bcd07a</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Generative AI Engineer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Afficiency</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MLflow, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=be5a298b53e539ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Smart Apply Test Company</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d697f334d121ec3</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81752facbba9d16c</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Senior Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Health Data Analytics Institute</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Dedham, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=073c59c0c666dd26</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (Oracle)</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Bitscopic</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, ELT, Git, Python</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7673be72cf2a7f02</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer – Enterprise, Data &amp; AI</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Zoox</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Foster City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, Terraform, Kubernetes, Airflow</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=303390f40d7bb17a</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Senior Data Integration Operations Engineerr</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Northeastern University</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Snowflake, Informatica PowerCenter, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=748fc639b3268939</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Senior AI &amp; Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e3b212b4def3f9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Consumer Cellular</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Scottsdale, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2545dd224fcef4a</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Sr. Cloud Security Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Inspira Financial</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Oak Brook, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=47913b36a9ddd604</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Data Engineer - &amp; Modeler Informatica</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aebf504e442ce2f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Full Stack Mid-level Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>WSFS Bank</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Wilmington, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Terraform, Kubernetes, Datadog, Python</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=78f65e99062ef281</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
           <t>Level 2 – Technical Support Engineer</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D56" t="n">
+      <c r="D70" t="n">
         <v>10.4</v>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, ELT, REST API integration</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=f92c2bb95c010dd6</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Bi Developer</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Cloud and Things</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Albany, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, Data Modeling, Star Schema, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b85dd5750a229b32</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-13.xlsx
+++ b/results/job_matches_2026-07-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Reliability Engineer, Battery Module</t>
+          <t>Sr. Machine Learning Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sparks, NV, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, GCP, BigQuery, Cloud Storage, Vertex AI, Spark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af907c177dd5fdb</t>
+          <t>https://www.indeed.com/viewjob?jk=c40b7d898d0faad8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AWS Data Engineering Advisor</t>
+          <t>Reliability Engineer, Battery Module</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ENGIE</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Sparks, NV, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Athena, S3, ECS, IAM, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=088581dbc2434494</t>
+          <t>https://www.indeed.com/viewjob?jk=3af907c177dd5fdb</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Engineering Architect</t>
+          <t>AWS Data Engineering Advisor</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>ENGIE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Kinesis, Athena, S3, ECS, IAM, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e831741c10ec9a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=088581dbc2434494</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SQL Developer</t>
+          <t>Engineering Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>We Are Recruiting</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Foley, AL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a0bb69f0f00f0c</t>
+          <t>https://www.indeed.com/viewjob?jk=e831741c10ec9a8d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>SQL Developer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Vytalize Health</t>
+          <t>We Are Recruiting</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Foley, AL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, IAM, RDS, Databricks, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439c58ad35a8bb78</t>
+          <t>https://www.indeed.com/viewjob?jk=39a0bb69f0f00f0c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Vytalize Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,24 +906,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, IAM, RDS, Databricks, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41b78df5b95306be</t>
+          <t>https://www.indeed.com/viewjob?jk=439c58ad35a8bb78</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26c2fa1d45c9055b</t>
+          <t>https://www.indeed.com/viewjob?jk=41b78df5b95306be</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Clifton, NJ, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Oracle</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009aa09bd21a9217</t>
+          <t>https://www.indeed.com/viewjob?jk=26c2fa1d45c9055b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Big Data)</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Clifton, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d8e19f0fb16bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=009aa09bd21a9217</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer II - Enterprise AI Products</t>
+          <t>Senior Software Engineer (Big Data)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dcac0248b7373d4</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d8e19f0fb16bc7</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Architect - C2H - Onsite</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TEEMA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7356e10af404cb1</t>
+          <t>https://www.indeed.com/viewjob?jk=898a5660007f1525</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Technical Specialist</t>
+          <t>Software Engineer II - Enterprise AI Products</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91e03219acd75f33</t>
+          <t>https://www.indeed.com/viewjob?jk=9dcac0248b7373d4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Technical Specialist(Python Developer)</t>
+          <t>Data Architect - C2H - Onsite</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>TEEMA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d26e04dc07674449</t>
+          <t>https://www.indeed.com/viewjob?jk=e7356e10af404cb1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer I-Pathology Molecular and Cell Based Medicine</t>
+          <t>Technical Specialist</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f1090f617db00fd</t>
+          <t>https://www.indeed.com/viewjob?jk=91e03219acd75f33</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer, Cat Digital</t>
+          <t>Technical Specialist(Python Developer)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, Snowflake, Power BI, CI/CD, Azure DevOps, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba56e26d2f7d66e</t>
+          <t>https://www.indeed.com/viewjob?jk=d26e04dc07674449</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior System Software Engineer for Cloud – GeForce NOW</t>
+          <t>Data Engineer I-Pathology Molecular and Cell Based Medicine</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, DynamoDB, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d6d30e78e6f4c6e</t>
+          <t>https://www.indeed.com/viewjob?jk=1f1090f617db00fd</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Data Engineer, Cat Digital</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>AWS, S3, Azure, Scala, Snowflake, Power BI, CI/CD, Azure DevOps, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd6388cdeebf986</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba56e26d2f7d66e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior System Software Engineer for Cloud – GeForce NOW</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, Azure, Scala, PostgreSQL, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, DynamoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=622d3a3e3c903762</t>
+          <t>https://www.indeed.com/viewjob?jk=9d6d30e78e6f4c6e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Technical Specialist - Senior</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cfb170c35e948ca</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd6388cdeebf986</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Technical Specialist - Senior</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,42 +1431,42 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, Lambda, Redshift, S3, Azure, Scala, PostgreSQL, MLOps, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51d97fe985e82f06</t>
+          <t>https://www.indeed.com/viewjob?jk=622d3a3e3c903762</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - GenAI/Agentic AI - Remote</t>
+          <t>Technical Specialist - Senior</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34b1a1a8543d5bde</t>
+          <t>https://www.indeed.com/viewjob?jk=9cfb170c35e948ca</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Big Data)</t>
+          <t>Senior Java Specialist</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Smart Apply Test Company</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Hive, Spark, Scala, Data Modeling, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17f9d9276b923717</t>
+          <t>https://www.indeed.com/viewjob?jk=51d97fe985e82f06</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Senior Data Scientist - GenAI/Agentic AI - Remote</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, HDFS, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3836b0fc7c4571</t>
+          <t>https://www.indeed.com/viewjob?jk=34b1a1a8543d5bde</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior Software Engineer (Big Data)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FirstDay Foundation</t>
+          <t>Smart Apply Test Company</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Databricks, Hadoop, Hive, Spark, Scala, Data Modeling, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d797cade2cc30f67</t>
+          <t>https://www.indeed.com/viewjob?jk=17f9d9276b923717</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NYSTEC</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, Databricks, Hadoop, HDFS, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e43f810dbefdcbc9</t>
+          <t>https://www.indeed.com/viewjob?jk=ad3836b0fc7c4571</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Building Service 32BJ Benefit Funds</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f681ba8c58e14f</t>
+          <t>https://www.indeed.com/viewjob?jk=6d7f6a3d55e28770</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Oracle OCI Cloud Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>FirstDay Foundation</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05cf4bb1193bec3f</t>
+          <t>https://www.indeed.com/viewjob?jk=d797cade2cc30f67</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>NYSTEC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Databricks, Unity Catalog, Spark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57668a6af42a8310</t>
+          <t>https://www.indeed.com/viewjob?jk=e43f810dbefdcbc9</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Managing Engineer - Fusion GRC Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, ELT, Splunk, CI/CD, Kubernetes, Git</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8c6087cd256e74</t>
+          <t>https://www.indeed.com/viewjob?jk=91f681ba8c58e14f</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Oracle OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Applied Medical</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Rancho Santa Margarita, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, YARN, SQL Server, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3004d47870448a1</t>
+          <t>https://www.indeed.com/viewjob?jk=05cf4bb1193bec3f</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, Glue, Redshift, RDS, Databricks, Unity Catalog, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=845986ee9c384d0c</t>
+          <t>https://www.indeed.com/viewjob?jk=57668a6af42a8310</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb9bc641ca30ce01</t>
+          <t>https://www.indeed.com/viewjob?jk=7bc63eb13d50f0ab</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. IT Data Engineer</t>
+          <t>Forward Deployed Engineer (AI) - Frisco, TX</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Invovia</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Hadoop, HBase, Scala, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0debfb86cec6f81</t>
+          <t>https://www.indeed.com/viewjob?jk=f8e491698172a68a</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Forward Deployed Engineer (AI)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>Invovia</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,102 +1931,102 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18e522d64598216a</t>
+          <t>https://www.indeed.com/viewjob?jk=9389c7fce7ffb417</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Applied Medical</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Rancho Santa Margarita, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
+          <t>AWS, RDS, Azure, YARN, SQL Server, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5962ad63a23cfa81</t>
+          <t>https://www.indeed.com/viewjob?jk=c3004d47870448a1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Threat Detection Engineer – Security Operations</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=083794db905029d1</t>
+          <t>https://www.indeed.com/viewjob?jk=845986ee9c384d0c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Marketing Technology Strategist</t>
+          <t>Threat Detection Engineer – Security Operations</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Phase2</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,59 +2036,59 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08cde2c4527579db</t>
+          <t>https://www.indeed.com/viewjob?jk=bb9bc641ca30ce01</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer - Oracle data integrator and BI</t>
+          <t>Managing Engineer - Fusion GRC Platform</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, ETL, ELT, Splunk, CI/CD, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b40de561865171b</t>
+          <t>https://www.indeed.com/viewjob?jk=fb8c6087cd256e74</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Engineer- Data &amp; Integration</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
+          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d4be214d89c9f3</t>
+          <t>https://www.indeed.com/viewjob?jk=cccab38c68c6dc6f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. IT Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
+          <t>API Gateway, RDS, Hadoop, HBase, Scala, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fd7b858f4e17691</t>
+          <t>https://www.indeed.com/viewjob?jk=d0debfb86cec6f81</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Solutions Architect - Financial Services (Hunter)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b1f7af295967ab5</t>
+          <t>https://www.indeed.com/viewjob?jk=18e522d64598216a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Security Architect(AI)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Paylocity</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, CI/CD, Kubernetes</t>
+          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ffe1515831234d9</t>
+          <t>https://www.indeed.com/viewjob?jk=5962ad63a23cfa81</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Product Engineer - Fusion GRC Platform</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, ELT, Splunk, CI/CD, Azure DevOps, Git</t>
+          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef44df6379fa49ce</t>
+          <t>https://www.indeed.com/viewjob?jk=083794db905029d1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Architect of Data Architecture</t>
+          <t>Marketing Technology Strategist</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Empower</t>
+          <t>Phase2</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a69b442d48a997e</t>
+          <t>https://www.indeed.com/viewjob?jk=08cde2c4527579db</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Master Data Management (MDM) Architect</t>
+          <t>Data Engineer - Oracle data integrator and BI</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, Databricks, GCP, Dataflow, Scala, Snowflake</t>
+          <t>RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d0e0294ddfbe996</t>
+          <t>https://www.indeed.com/viewjob?jk=4b40de561865171b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Architect / Quality Assurance Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>City of Philadelphia, PA</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,24 +2341,24 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d0882144e65f22c</t>
+          <t>https://www.indeed.com/viewjob?jk=14d4be214d89c9f3</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2376,17 +2376,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90454ed63602f69</t>
+          <t>https://www.indeed.com/viewjob?jk=3fd7b858f4e17691</t>
         </is>
       </c>
     </row>
@@ -2428,17 +2428,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Solutions Architect - Financial Services (Hunter)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Afficiency</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MLflow, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be5a298b53e539ed</t>
+          <t>https://www.indeed.com/viewjob?jk=4b1f7af295967ab5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Architect of Data Architecture</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Smart Apply Test Company</t>
+          <t>Empower</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, Redshift, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,67 +2491,67 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d697f334d121ec3</t>
+          <t>https://www.indeed.com/viewjob?jk=2a69b442d48a997e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Network Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81752facbba9d16c</t>
+          <t>https://www.indeed.com/viewjob?jk=bd021ef938d1ce24</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Security Architect(AI)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Health Data Analytics Institute</t>
+          <t>Paylocity</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dedham, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=073c59c0c666dd26</t>
+          <t>https://www.indeed.com/viewjob?jk=0ffe1515831234d9</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Oracle)</t>
+          <t>Product Engineer - Fusion GRC Platform</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, ETL, ELT, Splunk, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7673be72cf2a7f02</t>
+          <t>https://www.indeed.com/viewjob?jk=ef44df6379fa49ce</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise, Data &amp; AI</t>
+          <t>Senior Master Data Management (MDM) Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Zoox</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, Terraform, Kubernetes, Airflow</t>
+          <t>AWS, Glue, S3, RDS, Azure, Databricks, GCP, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303390f40d7bb17a</t>
+          <t>https://www.indeed.com/viewjob?jk=1d0e0294ddfbe996</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Integration Operations Engineerr</t>
+          <t>Data Architect / Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>City of Philadelphia, PA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Snowflake, Informatica PowerCenter, ETL, ELT</t>
+          <t>RDS, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,67 +2666,67 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=748fc639b3268939</t>
+          <t>https://www.indeed.com/viewjob?jk=2d0882144e65f22c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior AI &amp; Cloud Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e3b212b4def3f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=c90454ed63602f69</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Consumer Cellular</t>
+          <t>Afficiency</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MLflow, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2545dd224fcef4a</t>
+          <t>https://www.indeed.com/viewjob?jk=be5a298b53e539ed</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Cloud Security Engineer (Remote)</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Inspira Financial</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47913b36a9ddd604</t>
+          <t>https://www.indeed.com/viewjob?jk=5a2f1102b97c2bd1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer - &amp; Modeler Informatica</t>
+          <t>Data Engineer IV (Snowflake/Databricks) - REMOTE</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Velera</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aebf504e442ce2f2</t>
+          <t>https://www.indeed.com/viewjob?jk=fd204a1167efc6a3</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Full Stack Mid-level Java Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>WSFS Bank</t>
+          <t>Smart Apply Test Company</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Terraform, Kubernetes, Datadog, Python</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78f65e99062ef281</t>
+          <t>https://www.indeed.com/viewjob?jk=2d697f334d121ec3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Level 2 – Technical Support Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, ELT, REST API integration</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f92c2bb95c010dd6</t>
+          <t>https://www.indeed.com/viewjob?jk=81752facbba9d16c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Bi Developer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>Illumio</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,15 +2901,435 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5ce6ace065c9b44a</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Pano AI</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4aab6a4a6b438005</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Senior Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Health Data Analytics Institute</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Dedham, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=073c59c0c666dd26</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer (Oracle)</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Bitscopic</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, ELT, Git, Python</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7673be72cf2a7f02</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer – Enterprise, Data &amp; AI</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Zoox</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Foster City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, Terraform, Kubernetes, Airflow</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=303390f40d7bb17a</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Senior Data Integration Operations Engineerr</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Northeastern University</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Snowflake, Informatica PowerCenter, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=748fc639b3268939</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Senior AI &amp; Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e3b212b4def3f9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Consumer Cellular</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Scottsdale, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2545dd224fcef4a</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Sr. Cloud Security Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Inspira Financial</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Oak Brook, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=47913b36a9ddd604</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Data Engineer - &amp; Modeler Informatica</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aebf504e442ce2f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Level 2 – Technical Support Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, ELT, REST API integration</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f92c2bb95c010dd6</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Full Stack Mid-level Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>WSFS Bank</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Wilmington, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Terraform, Kubernetes, Datadog, Python</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=78f65e99062ef281</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Bi Developer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Cloud and Things</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Albany, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Oracle, SQL Server, Data Modeling, Star Schema, ETL, Power BI, Tableau</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b85dd5750a229b32</t>
         </is>

--- a/results/job_matches_2026-07-13.xlsx
+++ b/results/job_matches_2026-07-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DATABASE ADMINISTRATOR</t>
+          <t>Senior Data Management Professional - Data Engineering - Entities</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Versant Power</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bangor, ME, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
+          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,19 +671,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0bb056d66ba0554</t>
+          <t>https://www.indeed.com/viewjob?jk=44d437f6ae16eb4d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Quality AI Intern (61_2026.3)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Affinity Solutions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -692,46 +692,46 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Oracle, SQL Server</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2afd6091c64d55df</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc7c811d1c4b67c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Platform Engineer</t>
+          <t>AWS Severless Software Engineer III</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dave</t>
+          <t>NBME</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Cloud Storage, Vertex AI, Spark, Scala, Snowflake, MLOps</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, SQS, SNS, API Gateway, IAM</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40b7d898d0faad8</t>
+          <t>https://www.indeed.com/viewjob?jk=ce2dc4576aaa8a2e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Reliability Engineer, Battery Module</t>
+          <t>DATABASE ADMINISTRATOR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Versant Power</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sparks, NV, US USA</t>
+          <t>Bangor, ME, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af907c177dd5fdb</t>
+          <t>https://www.indeed.com/viewjob?jk=e0bb056d66ba0554</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AWS Data Engineering Advisor</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ENGIE</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,42 +801,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Athena, S3, ECS, IAM, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=088581dbc2434494</t>
+          <t>https://www.indeed.com/viewjob?jk=2afd6091c64d55df</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Engineering Architect</t>
+          <t>Sr. Machine Learning Platform Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, GCP, BigQuery, Cloud Storage, Vertex AI, Spark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e831741c10ec9a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=c40b7d898d0faad8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SQL Developer</t>
+          <t>Reliability Engineer, Battery Module</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>We Are Recruiting</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Foley, AL, US USA</t>
+          <t>Sparks, NV, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39a0bb69f0f00f0c</t>
+          <t>https://www.indeed.com/viewjob?jk=3af907c177dd5fdb</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>AI Native Builder_EU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vytalize Health</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, IAM, RDS, Databricks, CI/CD</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,172 +916,172 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439c58ad35a8bb78</t>
+          <t>https://www.indeed.com/viewjob?jk=0ea4fc6a360496ad</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Forward Deployed Engineer-Specialist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41b78df5b95306be</t>
+          <t>https://www.indeed.com/viewjob?jk=2df1f2e18d690c4a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Forward Deployed Engineer-Specialist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26c2fa1d45c9055b</t>
+          <t>https://www.indeed.com/viewjob?jk=d896c15ac717e14c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Forward Deployed Engineer-Specialist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Clifton, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Oracle</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009aa09bd21a9217</t>
+          <t>https://www.indeed.com/viewjob?jk=db4fe4e7c9a86b11</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Big Data)</t>
+          <t>AWS Data Engineering Advisor</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>ENGIE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Glue, Kinesis, Athena, S3, ECS, IAM, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d8e19f0fb16bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=088581dbc2434494</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=898a5660007f1525</t>
+          <t>https://www.indeed.com/viewjob?jk=6310ba46fd00a82c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Financial Data &amp; Analytics Engineer</t>
+          <t>Senior Data Engineer I</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The Research Foundation for The State University of New York at Stony Brook</t>
+          <t>C2FO</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Stony Brook, NY, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Glue, Redshift, Spark, Scala, Kafka, Data Modeling, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05c72e69c8d1b5df</t>
+          <t>https://www.indeed.com/viewjob?jk=e3a710f918b88f2b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer II - Enterprise AI Products</t>
+          <t>Engineering Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dcac0248b7373d4</t>
+          <t>https://www.indeed.com/viewjob?jk=e831741c10ec9a8d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Architect - C2H - Onsite</t>
+          <t>SQL Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TEEMA</t>
+          <t>We Are Recruiting</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>Foley, AL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, HDFS, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7356e10af404cb1</t>
+          <t>https://www.indeed.com/viewjob?jk=39a0bb69f0f00f0c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Technical Specialist</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Vytalize Health</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, IAM, RDS, Databricks, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91e03219acd75f33</t>
+          <t>https://www.indeed.com/viewjob?jk=439c58ad35a8bb78</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Technical Specialist(Python Developer)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,199 +1256,199 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d26e04dc07674449</t>
+          <t>https://www.indeed.com/viewjob?jk=41b78df5b95306be</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer I-Pathology Molecular and Cell Based Medicine</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f1090f617db00fd</t>
+          <t>https://www.indeed.com/viewjob?jk=26c2fa1d45c9055b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer, Cat Digital</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Clifton, NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Scala, Snowflake, Power BI, CI/CD, Azure DevOps, Airflow, Apache Airflow</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba56e26d2f7d66e</t>
+          <t>https://www.indeed.com/viewjob?jk=009aa09bd21a9217</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior System Software Engineer for Cloud – GeForce NOW</t>
+          <t>Senior Software Engineer (Big Data)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, DynamoDB, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d6d30e78e6f4c6e</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d8e19f0fb16bc7</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II - Enterprise AI Products</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd6388cdeebf986</t>
+          <t>https://www.indeed.com/viewjob?jk=9dcac0248b7373d4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Financial Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>The Research Foundation for The State University of New York at Stony Brook</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Stony Brook, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, Azure, Scala, PostgreSQL, MLOps, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=622d3a3e3c903762</t>
+          <t>https://www.indeed.com/viewjob?jk=05c72e69c8d1b5df</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Technical Specialist - Senior</t>
+          <t>Technical Specialist</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1462,7 +1462,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1476,14 +1476,14 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cfb170c35e948ca</t>
+          <t>https://www.indeed.com/viewjob?jk=91e03219acd75f33</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Java Specialist</t>
+          <t>Technical Specialist(Python Developer)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1497,7 +1497,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51d97fe985e82f06</t>
+          <t>https://www.indeed.com/viewjob?jk=d26e04dc07674449</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - GenAI/Agentic AI - Remote</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, Power BI</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34b1a1a8543d5bde</t>
+          <t>https://www.indeed.com/viewjob?jk=898a5660007f1525</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Big Data)</t>
+          <t>Data Engineer I-Pathology Molecular and Cell Based Medicine</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Smart Apply Test Company</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Hive, Spark, Scala, Data Modeling, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,67 +1581,67 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17f9d9276b923717</t>
+          <t>https://www.indeed.com/viewjob?jk=1f1090f617db00fd</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Analytics Data Engineer, Cat Digital</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, HDFS, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, Scala, Snowflake, Power BI, CI/CD, Azure DevOps, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3836b0fc7c4571</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba56e26d2f7d66e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Azure DevOps Engineer</t>
+          <t>Senior System Software Engineer for Cloud – GeForce NOW</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Building Service 32BJ Benefit Funds</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, DynamoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,67 +1651,67 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d7f6a3d55e28770</t>
+          <t>https://www.indeed.com/viewjob?jk=9d6d30e78e6f4c6e</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FirstDay Foundation</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d797cade2cc30f67</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd6388cdeebf986</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Technical Specialist - Senior</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NYSTEC</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e43f810dbefdcbc9</t>
+          <t>https://www.indeed.com/viewjob?jk=9cfb170c35e948ca</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Java Specialist</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f681ba8c58e14f</t>
+          <t>https://www.indeed.com/viewjob?jk=51d97fe985e82f06</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Oracle OCI Cloud Engineer</t>
+          <t>Senior Data Scientist - GenAI/Agentic AI - Remote</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05cf4bb1193bec3f</t>
+          <t>https://www.indeed.com/viewjob?jk=34b1a1a8543d5bde</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer (Big Data)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Smart Apply Test Company</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Databricks, Unity Catalog, Spark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Hadoop, Hive, Spark, Scala, Data Modeling, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57668a6af42a8310</t>
+          <t>https://www.indeed.com/viewjob?jk=17f9d9276b923717</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Databricks, Hadoop, HDFS, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bc63eb13d50f0ab</t>
+          <t>https://www.indeed.com/viewjob?jk=ad3836b0fc7c4571</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (AI) - Frisco, TX</t>
+          <t>Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Invovia</t>
+          <t>Building Service 32BJ Benefit Funds</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, ETL, ELT, MLOps</t>
+          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8e491698172a68a</t>
+          <t>https://www.indeed.com/viewjob?jk=6d7f6a3d55e28770</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (AI)</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Invovia</t>
+          <t>FirstDay Foundation</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, ETL, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9389c7fce7ffb417</t>
+          <t>https://www.indeed.com/viewjob?jk=d797cade2cc30f67</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Applied Medical</t>
+          <t>NYSTEC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Rancho Santa Margarita, CA, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, YARN, SQL Server, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3004d47870448a1</t>
+          <t>https://www.indeed.com/viewjob?jk=e43f810dbefdcbc9</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=845986ee9c384d0c</t>
+          <t>https://www.indeed.com/viewjob?jk=91f681ba8c58e14f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Oracle OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb9bc641ca30ce01</t>
+          <t>https://www.indeed.com/viewjob?jk=05cf4bb1193bec3f</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Managing Engineer - Fusion GRC Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,42 +2061,42 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, ELT, Splunk, CI/CD, Kubernetes, Git</t>
+          <t>AWS, Glue, Redshift, RDS, Databricks, Unity Catalog, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8c6087cd256e74</t>
+          <t>https://www.indeed.com/viewjob?jk=57668a6af42a8310</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer- Data &amp; Integration</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>Hightower Advisors</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cccab38c68c6dc6f</t>
+          <t>https://www.indeed.com/viewjob?jk=487e755470e0a906</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. IT Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Hadoop, HBase, Scala, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0debfb86cec6f81</t>
+          <t>https://www.indeed.com/viewjob?jk=7bc63eb13d50f0ab</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Forward Deployed Engineer (AI) - Frisco, TX</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>Invovia</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,102 +2176,102 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18e522d64598216a</t>
+          <t>https://www.indeed.com/viewjob?jk=f8e491698172a68a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Forward Deployed Engineer (AI)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Invovia</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5962ad63a23cfa81</t>
+          <t>https://www.indeed.com/viewjob?jk=9389c7fce7ffb417</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Applied Medical</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Rancho Santa Margarita, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
+          <t>AWS, RDS, Azure, YARN, SQL Server, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=083794db905029d1</t>
+          <t>https://www.indeed.com/viewjob?jk=c3004d47870448a1</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Marketing Technology Strategist</t>
+          <t>Threat Detection Engineer – Security Operations</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Phase2</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,94 +2281,94 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08cde2c4527579db</t>
+          <t>https://www.indeed.com/viewjob?jk=845986ee9c384d0c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer - Oracle data integrator and BI</t>
+          <t>Threat Detection Engineer – Security Operations</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b40de561865171b</t>
+          <t>https://www.indeed.com/viewjob?jk=bb9bc641ca30ce01</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Managing Engineer - Fusion GRC Platform</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, ETL, ELT, Splunk, CI/CD, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d4be214d89c9f3</t>
+          <t>https://www.indeed.com/viewjob?jk=fb8c6087cd256e74</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Engineer- Data &amp; Integration</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
+          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fd7b858f4e17691</t>
+          <t>https://www.indeed.com/viewjob?jk=cccab38c68c6dc6f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer - SRE</t>
+          <t>Sr. IT Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>API Gateway, RDS, Hadoop, HBase, Scala, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f2cb5787bcd07a</t>
+          <t>https://www.indeed.com/viewjob?jk=d0debfb86cec6f81</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Solutions Architect - Financial Services (Hunter)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b1f7af295967ab5</t>
+          <t>https://www.indeed.com/viewjob?jk=18e522d64598216a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Architect of Data Architecture</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Empower</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a69b442d48a997e</t>
+          <t>https://www.indeed.com/viewjob?jk=5962ad63a23cfa81</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Network Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Splunk, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd021ef938d1ce24</t>
+          <t>https://www.indeed.com/viewjob?jk=083794db905029d1</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Security Architect(AI)</t>
+          <t>Marketing Technology Strategist</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Paylocity</t>
+          <t>Phase2</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, CI/CD, Kubernetes</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ffe1515831234d9</t>
+          <t>https://www.indeed.com/viewjob?jk=08cde2c4527579db</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Product Engineer - Fusion GRC Platform</t>
+          <t>Data Engineer - Oracle data integrator and BI</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, ELT, Splunk, CI/CD, Azure DevOps, Git</t>
+          <t>RDS, Azure, Scala, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef44df6379fa49ce</t>
+          <t>https://www.indeed.com/viewjob?jk=4b40de561865171b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Master Data Management (MDM) Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Azure, Databricks, GCP, Dataflow, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d0e0294ddfbe996</t>
+          <t>https://www.indeed.com/viewjob?jk=14d4be214d89c9f3</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Architect / Quality Assurance Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>City of Philadelphia, PA</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d0882144e65f22c</t>
+          <t>https://www.indeed.com/viewjob?jk=3fd7b858f4e17691</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Security Architect(AI)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Paylocity</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90454ed63602f69</t>
+          <t>https://www.indeed.com/viewjob?jk=7b6040d8fca19b2e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Network Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Afficiency</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MLflow, Terraform, Docker</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Splunk, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be5a298b53e539ed</t>
+          <t>https://www.indeed.com/viewjob?jk=bd021ef938d1ce24</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Solutions Architect - Financial Services (Hunter)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Spark, Scala, Kafka, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a2f1102b97c2bd1</t>
+          <t>https://www.indeed.com/viewjob?jk=4b1f7af295967ab5</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer IV (Snowflake/Databricks) - REMOTE</t>
+          <t>Senior Security Architect(AI)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Velera</t>
+          <t>Paylocity</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, Snowflake, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd204a1167efc6a3</t>
+          <t>https://www.indeed.com/viewjob?jk=0ffe1515831234d9</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Product Engineer - Fusion GRC Platform</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Smart Apply Test Company</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, ETL, ELT, Splunk, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,67 +2841,67 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d697f334d121ec3</t>
+          <t>https://www.indeed.com/viewjob?jk=ef44df6379fa49ce</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Architect of Data Architecture</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Empower</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, Redshift, RDS, Spark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81752facbba9d16c</t>
+          <t>https://www.indeed.com/viewjob?jk=2a69b442d48a997e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr. Site Reliability Engineer</t>
+          <t>Senior Master Data Management (MDM) Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Illumio</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, S3, RDS, Azure, Databricks, GCP, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ce6ace065c9b44a</t>
+          <t>https://www.indeed.com/viewjob?jk=1d0e0294ddfbe996</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Data Architect / Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Pano AI</t>
+          <t>City of Philadelphia, PA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform</t>
+          <t>RDS, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,67 +2946,67 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aab6a4a6b438005</t>
+          <t>https://www.indeed.com/viewjob?jk=2d0882144e65f22c</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Health Data Analytics Institute</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dedham, MA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
+          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=073c59c0c666dd26</t>
+          <t>https://www.indeed.com/viewjob?jk=c90454ed63602f69</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Oracle)</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>Afficiency</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MLflow, Terraform, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7673be72cf2a7f02</t>
+          <t>https://www.indeed.com/viewjob?jk=be5a298b53e539ed</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise, Data &amp; AI</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Zoox</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, Terraform, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303390f40d7bb17a</t>
+          <t>https://www.indeed.com/viewjob?jk=5a2f1102b97c2bd1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Integration Operations Engineerr</t>
+          <t>Site Reliability Engineer - SRE</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Bitscopic</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Snowflake, Informatica PowerCenter, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=748fc639b3268939</t>
+          <t>https://www.indeed.com/viewjob?jk=91f2cb5787bcd07a</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior AI &amp; Cloud Engineer</t>
+          <t>Data Engineer IV (Snowflake/Databricks) - REMOTE</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Velera</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e3b212b4def3f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=fd204a1167efc6a3</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Consumer Cellular</t>
+          <t>Smart Apply Test Company</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2545dd224fcef4a</t>
+          <t>https://www.indeed.com/viewjob?jk=2d697f334d121ec3</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. Cloud Security Engineer (Remote)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Inspira Financial</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47913b36a9ddd604</t>
+          <t>https://www.indeed.com/viewjob?jk=81752facbba9d16c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer - &amp; Modeler Informatica</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Pano AI</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aebf504e442ce2f2</t>
+          <t>https://www.indeed.com/viewjob?jk=4aab6a4a6b438005</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Level 2 – Technical Support Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Health Data Analytics Institute</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dedham, MA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, ELT, REST API integration</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f92c2bb95c010dd6</t>
+          <t>https://www.indeed.com/viewjob?jk=073c59c0c666dd26</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Full Stack Mid-level Java Software Engineer</t>
+          <t>Senior Data Engineer (Oracle)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>WSFS Bank</t>
+          <t>Bitscopic</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Terraform, Kubernetes, Datadog, Python</t>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78f65e99062ef281</t>
+          <t>https://www.indeed.com/viewjob?jk=7673be72cf2a7f02</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Bi Developer</t>
+          <t>Senior Data Engineer – Enterprise, Data &amp; AI</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>Zoox</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,17 +3321,332 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
+          <t>RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, Terraform, Kubernetes, Airflow</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=303390f40d7bb17a</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Senior Data Integration Operations Engineerr</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Northeastern University</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Snowflake, Informatica PowerCenter, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=748fc639b3268939</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Senior AI &amp; Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e3b212b4def3f9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Cloud Architect @ Dallas, TX</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Logistic Solutions Inc</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a1ffb721ba3a7f68</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Consumer Cellular</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Scottsdale, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2545dd224fcef4a</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Sr. Cloud Security Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Inspira Financial</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Oak Brook, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=47913b36a9ddd604</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Data Engineer - &amp; Modeler Informatica</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aebf504e442ce2f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Bi Developer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Cloud and Things</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Albany, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Oracle, SQL Server, Data Modeling, Star Schema, ETL, Power BI, Tableau</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b85dd5750a229b32</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Level 2 – Technical Support Engineer</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, ELT, REST API integration</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f92c2bb95c010dd6</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Full Stack Mid-level Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>WSFS Bank</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Wilmington, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Terraform, Kubernetes, Datadog, Python</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=78f65e99062ef281</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-13.xlsx
+++ b/results/job_matches_2026-07-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Machine Learning Platform Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, GCP, BigQuery, Cloud Storage, Vertex AI, Spark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2afd6091c64d55df</t>
+          <t>https://www.indeed.com/viewjob?jk=c40b7d898d0faad8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Platform Engineer</t>
+          <t>Reliability Engineer, Battery Module</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dave</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sparks, NV, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Cloud Storage, Vertex AI, Spark, Scala, Snowflake, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40b7d898d0faad8</t>
+          <t>https://www.indeed.com/viewjob?jk=3af907c177dd5fdb</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Reliability Engineer, Battery Module</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sparks, NV, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,17 +871,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3af907c177dd5fdb</t>
+          <t>https://www.indeed.com/viewjob?jk=2afd6091c64d55df</t>
         </is>
       </c>
     </row>
@@ -1203,17 +1203,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Vytalize Health</t>
+          <t>Safelite</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, IAM, RDS, Databricks, CI/CD</t>
+          <t>AWS, RDS, BigQuery, Scala, Snowflake, Oracle, SQL Server, ETL, ELT, Talend</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439c58ad35a8bb78</t>
+          <t>https://www.indeed.com/viewjob?jk=eab9b545c0f88523</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Vytalize Health</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,24 +1256,24 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, IAM, RDS, Databricks, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41b78df5b95306be</t>
+          <t>https://www.indeed.com/viewjob?jk=439c58ad35a8bb78</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26c2fa1d45c9055b</t>
+          <t>https://www.indeed.com/viewjob?jk=41b78df5b95306be</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Clifton, NJ, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Oracle</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009aa09bd21a9217</t>
+          <t>https://www.indeed.com/viewjob?jk=26c2fa1d45c9055b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Big Data)</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Clifton, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, Databricks, Unity Catalog, Hadoop, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d8e19f0fb16bc7</t>
+          <t>https://www.indeed.com/viewjob?jk=009aa09bd21a9217</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer II - Enterprise AI Products</t>
+          <t>Senior Software Engineer (Big Data)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Hadoop, Hive, Spark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dcac0248b7373d4</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d8e19f0fb16bc7</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Financial Data &amp; Analytics Engineer</t>
+          <t>Software Engineer II - Enterprise AI Products</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The Research Foundation for The State University of New York at Stony Brook</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Stony Brook, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05c72e69c8d1b5df</t>
+          <t>https://www.indeed.com/viewjob?jk=9dcac0248b7373d4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Technical Specialist</t>
+          <t>Senior Financial Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>The Research Foundation for The State University of New York at Stony Brook</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Stony Brook, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91e03219acd75f33</t>
+          <t>https://www.indeed.com/viewjob?jk=05c72e69c8d1b5df</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Technical Specialist(Python Developer)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d26e04dc07674449</t>
+          <t>https://www.indeed.com/viewjob?jk=898a5660007f1525</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Technical Specialist</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=898a5660007f1525</t>
+          <t>https://www.indeed.com/viewjob?jk=91e03219acd75f33</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer I-Pathology Molecular and Cell Based Medicine</t>
+          <t>Technical Specialist(Python Developer)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f1090f617db00fd</t>
+          <t>https://www.indeed.com/viewjob?jk=d26e04dc07674449</t>
         </is>
       </c>
     </row>
@@ -1623,17 +1623,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior System Software Engineer for Cloud – GeForce NOW</t>
+          <t>Data Engineer I-Pathology Molecular and Cell Based Medicine</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, DynamoDB, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d6d30e78e6f4c6e</t>
+          <t>https://www.indeed.com/viewjob?jk=1f1090f617db00fd</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior System Software Engineer for Cloud – GeForce NOW</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, DynamoDB, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dd6388cdeebf986</t>
+          <t>https://www.indeed.com/viewjob?jk=9d6d30e78e6f4c6e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Technical Specialist - Senior</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,29 +1711,29 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cfb170c35e948ca</t>
+          <t>https://www.indeed.com/viewjob?jk=2dd6388cdeebf986</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Java Specialist</t>
+          <t>Technical Specialist - Senior</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51d97fe985e82f06</t>
+          <t>https://www.indeed.com/viewjob?jk=9cfb170c35e948ca</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - GenAI/Agentic AI - Remote</t>
+          <t>Senior Java Specialist</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34b1a1a8543d5bde</t>
+          <t>https://www.indeed.com/viewjob?jk=51d97fe985e82f06</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Big Data)</t>
+          <t>Azure DevOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Smart Apply Test Company</t>
+          <t>Building Service 32BJ Benefit Funds</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Hadoop, Hive, Spark, Scala, Data Modeling, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17f9d9276b923717</t>
+          <t>https://www.indeed.com/viewjob?jk=6d7f6a3d55e28770</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Solutions Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>FirstDay Foundation</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, HDFS, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad3836b0fc7c4571</t>
+          <t>https://www.indeed.com/viewjob?jk=d797cade2cc30f67</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Azure DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Building Service 32BJ Benefit Funds</t>
+          <t>NYSTEC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d7f6a3d55e28770</t>
+          <t>https://www.indeed.com/viewjob?jk=e43f810dbefdcbc9</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FirstDay Foundation</t>
+          <t>Cornell University</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Ithaca, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d797cade2cc30f67</t>
+          <t>https://www.indeed.com/viewjob?jk=91f681ba8c58e14f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer (Big Data)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NYSTEC</t>
+          <t>Smart Apply Test Company</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Data Lake Storage, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Databricks, Hadoop, Hive, Spark, Scala, Data Modeling, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e43f810dbefdcbc9</t>
+          <t>https://www.indeed.com/viewjob?jk=17f9d9276b923717</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Oracle OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cornell University</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ithaca, NY, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, Athena, S3, RDS, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f681ba8c58e14f</t>
+          <t>https://www.indeed.com/viewjob?jk=05cf4bb1193bec3f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Oracle OCI Cloud Engineer</t>
+          <t>Data Solutions Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,17 +2026,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Databricks, Hadoop, HDFS, Spark, Scala, Kafka, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05cf4bb1193bec3f</t>
+          <t>https://www.indeed.com/viewjob?jk=ad3836b0fc7c4571</t>
         </is>
       </c>
     </row>
@@ -2078,17 +2078,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Data Scientist - GenAI/Agentic AI - Remote</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Hightower Advisors</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Hadoop, Spark, Scala, Snowflake, NoSQL, ETL, Power BI</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=487e755470e0a906</t>
+          <t>https://www.indeed.com/viewjob?jk=34b1a1a8543d5bde</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Engineering Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bc63eb13d50f0ab</t>
+          <t>https://www.indeed.com/viewjob?jk=8a16e3ffc1c278fc</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (AI) - Frisco, TX</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Invovia</t>
+          <t>Hightower Advisors</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, ETL, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8e491698172a68a</t>
+          <t>https://www.indeed.com/viewjob?jk=487e755470e0a906</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (AI)</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Invovia</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, ETL, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9389c7fce7ffb417</t>
+          <t>https://www.indeed.com/viewjob?jk=7bc63eb13d50f0ab</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Forward Deployed Engineer (AI) - Frisco, TX</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Applied Medical</t>
+          <t>Invovia</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Rancho Santa Margarita, CA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, YARN, SQL Server, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3004d47870448a1</t>
+          <t>https://www.indeed.com/viewjob?jk=f8e491698172a68a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Forward Deployed Engineer (AI)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Invovia</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Scala, Snowflake, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=845986ee9c384d0c</t>
+          <t>https://www.indeed.com/viewjob?jk=9389c7fce7ffb417</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Applied Medical</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Rancho Santa Margarita, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, YARN, SQL Server, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb9bc641ca30ce01</t>
+          <t>https://www.indeed.com/viewjob?jk=c3004d47870448a1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Managing Engineer - Fusion GRC Platform</t>
+          <t>Threat Detection Engineer – Security Operations</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, ELT, Splunk, CI/CD, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8c6087cd256e74</t>
+          <t>https://www.indeed.com/viewjob?jk=845986ee9c384d0c</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer- Data &amp; Integration</t>
+          <t>Threat Detection Engineer – Security Operations</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Pacific Life</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Snowflake, Splunk, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cccab38c68c6dc6f</t>
+          <t>https://www.indeed.com/viewjob?jk=bb9bc641ca30ce01</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. IT Data Engineer</t>
+          <t>Managing Engineer - Fusion GRC Platform</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Hadoop, HBase, Scala, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Scala, ETL, ELT, Splunk, CI/CD, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0debfb86cec6f81</t>
+          <t>https://www.indeed.com/viewjob?jk=fb8c6087cd256e74</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Software Engineer- Data &amp; Integration</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Stellar Solutions</t>
+          <t>Pacific Life</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, CI/CD</t>
+          <t>Azure, Scala, Snowflake, Oracle, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18e522d64598216a</t>
+          <t>https://www.indeed.com/viewjob?jk=cccab38c68c6dc6f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Marketing Technology Strategist</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Phase2</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5962ad63a23cfa81</t>
+          <t>https://www.indeed.com/viewjob?jk=08cde2c4527579db</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. IT Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
+          <t>API Gateway, RDS, Hadoop, HBase, Scala, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=083794db905029d1</t>
+          <t>https://www.indeed.com/viewjob?jk=d0debfb86cec6f81</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Marketing Technology Strategist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Phase2</t>
+          <t>Stellar Solutions</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08cde2c4527579db</t>
+          <t>https://www.indeed.com/viewjob?jk=18e522d64598216a</t>
         </is>
       </c>
     </row>
@@ -2603,17 +2603,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14d4be214d89c9f3</t>
+          <t>https://www.indeed.com/viewjob?jk=5962ad63a23cfa81</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,17 +2656,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Hadoop, HBase, Spark, Scala, Data Modeling, ETL, Maven, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fd7b858f4e17691</t>
+          <t>https://www.indeed.com/viewjob?jk=083794db905029d1</t>
         </is>
       </c>
     </row>
@@ -2918,17 +2918,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Architect / Quality Assurance Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>City of Philadelphia, PA</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,24 +2936,24 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Airflow, Git</t>
+          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d0882144e65f22c</t>
+          <t>https://www.indeed.com/viewjob?jk=c90454ed63602f69</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, MongoDB, NoSQL, CI/CD, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90454ed63602f69</t>
+          <t>https://www.indeed.com/viewjob?jk=14d4be214d89c9f3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Afficiency</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MLflow, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, MongoDB, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be5a298b53e539ed</t>
+          <t>https://www.indeed.com/viewjob?jk=3fd7b858f4e17691</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Senior Software Engineer - Backend (Python &amp; AWS)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, IAM, RDS, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a2f1102b97c2bd1</t>
+          <t>https://www.indeed.com/viewjob?jk=7f6911722171aa1c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer - SRE</t>
+          <t>Data Architect / Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>City of Philadelphia, PA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f2cb5787bcd07a</t>
+          <t>https://www.indeed.com/viewjob?jk=2d0882144e65f22c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer IV (Snowflake/Databricks) - REMOTE</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Velera</t>
+          <t>Afficiency</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, MLflow, Terraform, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd204a1167efc6a3</t>
+          <t>https://www.indeed.com/viewjob?jk=be5a298b53e539ed</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Smart Apply Test Company</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, NoSQL, Data Modeling, CI/CD, Jenkins, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,59 +3156,59 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d697f334d121ec3</t>
+          <t>https://www.indeed.com/viewjob?jk=5a2f1102b97c2bd1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Site Reliability Engineer - SRE</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Bitscopic</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, ETL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81752facbba9d16c</t>
+          <t>https://www.indeed.com/viewjob?jk=91f2cb5787bcd07a</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior Business Intelligence Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Pano AI</t>
+          <t>Safelite</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, BigQuery, Scala, Snowflake, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aab6a4a6b438005</t>
+          <t>https://www.indeed.com/viewjob?jk=89f11f71a1c806a8</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Engineer IV (Snowflake/Databricks) - REMOTE</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Health Data Analytics Institute</t>
+          <t>Velera</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Dedham, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,19 +3261,19 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=073c59c0c666dd26</t>
+          <t>https://www.indeed.com/viewjob?jk=fd204a1167efc6a3</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Oracle)</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Bitscopic</t>
+          <t>Pano AI</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7673be72cf2a7f02</t>
+          <t>https://www.indeed.com/viewjob?jk=4aab6a4a6b438005</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise, Data &amp; AI</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Zoox</t>
+          <t>Health Data Analytics Institute</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Dedham, MA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, Terraform, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303390f40d7bb17a</t>
+          <t>https://www.indeed.com/viewjob?jk=073c59c0c666dd26</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Integration Operations Engineerr</t>
+          <t>Senior Data Engineer (Oracle)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>Bitscopic</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Snowflake, Informatica PowerCenter, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Oracle, PostgreSQL, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=748fc639b3268939</t>
+          <t>https://www.indeed.com/viewjob?jk=7673be72cf2a7f02</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior AI &amp; Cloud Engineer</t>
+          <t>Senior Data Engineer – Enterprise, Data &amp; AI</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Zoox</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
+          <t>RDS, Databricks, BigQuery, Scala, Snowflake, ETL, ELT, Terraform, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e3b212b4def3f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=303390f40d7bb17a</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Cloud Architect @ Dallas, TX</t>
+          <t>Senior Data Integration Operations Engineerr</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Logistic Solutions Inc</t>
+          <t>Northeastern University</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Snowflake, Informatica PowerCenter, ETL, ELT</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1ffb721ba3a7f68</t>
+          <t>https://www.indeed.com/viewjob?jk=748fc639b3268939</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Consumer Cellular</t>
+          <t>Smart Apply Test Company</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2545dd224fcef4a</t>
+          <t>https://www.indeed.com/viewjob?jk=2d697f334d121ec3</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr. Cloud Security Engineer (Remote)</t>
+          <t>Senior AI &amp; Cloud Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Inspira Financial</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+          <t>Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, ELT, MLflow, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47913b36a9ddd604</t>
+          <t>https://www.indeed.com/viewjob?jk=8e3b212b4def3f9f</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer - &amp; Modeler Informatica</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aebf504e442ce2f2</t>
+          <t>https://www.indeed.com/viewjob?jk=81752facbba9d16c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Bi Developer</t>
+          <t>Sr. Data Engineering Architect</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, Data Modeling, Star Schema, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, DataOps</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b85dd5750a229b32</t>
+          <t>https://www.indeed.com/viewjob?jk=b6af42e024fb5358</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Level 2 – Technical Support Engineer</t>
+          <t>Cloud Architect @ Dallas, TX</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Logistic Solutions Inc</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, ELT, REST API integration</t>
+          <t>AWS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, CI/CD, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f92c2bb95c010dd6</t>
+          <t>https://www.indeed.com/viewjob?jk=a1ffb721ba3a7f68</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Full Stack Mid-level Java Software Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>WSFS Bank</t>
+          <t>Consumer Cellular</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,15 +3636,225 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2545dd224fcef4a</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Sr. Cloud Security Engineer (Remote)</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Inspira Financial</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Oak Brook, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Azure, SQL Server, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=47913b36a9ddd604</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Data Engineer - &amp; Modeler Informatica</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Azure, Databricks, Spark, Scala, Snowflake, Data Modeling, ETL, ELT, Git, Python</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aebf504e442ce2f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Insight</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Chandler, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, GCP, Scala, Data Modeling, ETL, ELT, Power BI, Git</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=445e8b11f533b240</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Level 2 – Technical Support Engineer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Snowflake, Databricks Lakehouse, ELT, REST API integration</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f92c2bb95c010dd6</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Bi Developer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Cloud and Things</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Albany, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, Data Modeling, Star Schema, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b85dd5750a229b32</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Full Stack Mid-level Java Software Engineer</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>WSFS Bank</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Wilmington, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Scala, NoSQL, CI/CD, Terraform, Kubernetes, Datadog, Python</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=78f65e99062ef281</t>
         </is>
